--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-21).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-21).xlsx
@@ -935,10 +935,10 @@
     <t>214</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>R$ 3.061,81</t>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R$ 3.054,77</t>
   </si>
   <si>
     <t>34.9</t>
@@ -947,10 +947,10 @@
     <t>21.7</t>
   </si>
   <si>
-    <t>4.69</t>
-  </si>
-  <si>
-    <t>18.0</t>
+    <t>4.68</t>
+  </si>
+  <si>
+    <t>17.9</t>
   </si>
   <si>
     <t>6.6</t>
@@ -959,7 +959,7 @@
     <t>5.9</t>
   </si>
   <si>
-    <t>45.3%</t>
+    <t>45.8%</t>
   </si>
   <si>
     <t>19.1%</t>
@@ -986,25 +986,25 @@
     <t>3.4%</t>
   </si>
   <si>
-    <t>904.0</t>
-  </si>
-  <si>
-    <t>727.0</t>
-  </si>
-  <si>
-    <t>80.0</t>
+    <t>907.0</t>
+  </si>
+  <si>
+    <t>730.0</t>
+  </si>
+  <si>
+    <t>81.0</t>
   </si>
   <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>205.0</t>
+    <t>206.0</t>
   </si>
   <si>
     <t>48.0</t>
   </si>
   <si>
-    <t>289.0</t>
+    <t>290.0</t>
   </si>
   <si>
     <t>125.0</t>
@@ -9989,7 +9989,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10019,14 +10019,26 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>3495.5100000000002</v>
+      </c>
+      <c r="N58" s="6">
+        <v>47</v>
+      </c>
       <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>3.3507400000000001</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>18.794087096774195</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.8086032258064515</v>
+      </c>
       <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.32258064516129031</v>
+      </c>
       <c r="U58" s="9"/>
       <c r="V58" s="9"/>
       <c r="W58" s="9"/>
@@ -26775,7 +26787,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>51</v>
@@ -26805,35 +26817,93 @@
         <v>58</v>
       </c>
       <c r="L172" s="4"/>
-      <c r="M172" s="5"/>
-      <c r="N172" s="6"/>
-      <c r="O172" s="6"/>
-      <c r="P172" s="7"/>
-      <c r="Q172" s="8"/>
-      <c r="R172" s="8"/>
-      <c r="S172" s="8"/>
-      <c r="T172" s="9"/>
-      <c r="U172" s="9"/>
-      <c r="V172" s="9"/>
-      <c r="W172" s="9"/>
-      <c r="X172" s="9"/>
-      <c r="Y172" s="9"/>
-      <c r="Z172" s="9"/>
-      <c r="AA172" s="9"/>
-      <c r="AB172" s="9"/>
-      <c r="AC172" s="9"/>
-      <c r="AD172" s="6"/>
-      <c r="AE172" s="6"/>
-      <c r="AF172" s="6"/>
-      <c r="AG172" s="6"/>
-      <c r="AH172" s="6"/>
-      <c r="AI172" s="6"/>
-      <c r="AJ172" s="6"/>
-      <c r="AK172" s="6"/>
-      <c r="AL172" s="6"/>
-      <c r="AM172" s="6"/>
-      <c r="AN172" s="9"/>
-      <c r="AO172" s="6"/>
+      <c r="M172" s="5">
+        <v>1544.3</v>
+      </c>
+      <c r="N172" s="6">
+        <v>19</v>
+      </c>
+      <c r="O172" s="6">
+        <v>16</v>
+      </c>
+      <c r="P172" s="7">
+        <v>3.9271947368421052</v>
+      </c>
+      <c r="Q172" s="8">
+        <v>17.329168750000001</v>
+      </c>
+      <c r="R172" s="8">
+        <v>6.71875</v>
+      </c>
+      <c r="S172" s="8">
+        <v>7</v>
+      </c>
+      <c r="T172" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="U172" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="V172" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="W172" s="9">
+        <v>0</v>
+      </c>
+      <c r="X172" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Y172" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD172" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO172" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP172" s="4">
         <v>58</v>
       </c>
@@ -30106,7 +30176,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -30136,14 +30206,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>2878.6199999999999</v>
+      </c>
+      <c r="N195" s="6">
+        <v>34</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>5.1057281249999997</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>15.848552173913044</v>
+      </c>
+      <c r="R195" s="8">
+        <v>3.9586956521739127</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.47826086956521741</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-21).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-21).xlsx
@@ -935,16 +935,16 @@
     <t>214</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 3.054,77</t>
-  </si>
-  <si>
-    <t>34.9</t>
-  </si>
-  <si>
-    <t>21.7</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 3.070,92</t>
+  </si>
+  <si>
+    <t>35.1</t>
+  </si>
+  <si>
+    <t>21.9</t>
   </si>
   <si>
     <t>4.68</t>
@@ -956,13 +956,13 @@
     <t>6.6</t>
   </si>
   <si>
-    <t>5.9</t>
-  </si>
-  <si>
-    <t>45.8%</t>
-  </si>
-  <si>
-    <t>19.1%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>45.3%</t>
+  </si>
+  <si>
+    <t>19.0%</t>
   </si>
   <si>
     <t>2.1%</t>
@@ -971,10 +971,10 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.4%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
+    <t>5.3%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>7.6%</t>
@@ -983,34 +983,28 @@
     <t>3.3%</t>
   </si>
   <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>907.0</t>
-  </si>
-  <si>
-    <t>730.0</t>
-  </si>
-  <si>
-    <t>81.0</t>
+    <t>933.0</t>
+  </si>
+  <si>
+    <t>754.0</t>
+  </si>
+  <si>
+    <t>82.0</t>
   </si>
   <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>206.0</t>
-  </si>
-  <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>290.0</t>
-  </si>
-  <si>
-    <t>125.0</t>
-  </si>
-  <si>
-    <t>129.0</t>
+    <t>211.0</t>
+  </si>
+  <si>
+    <t>49.0</t>
+  </si>
+  <si>
+    <t>301.0</t>
+  </si>
+  <si>
+    <t>131.0</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -3236,7 +3230,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3266,35 +3260,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>5584.54</v>
+      </c>
+      <c r="N13" s="6">
+        <v>66</v>
+      </c>
+      <c r="O13" s="6">
+        <v>51</v>
+      </c>
+      <c r="P13" s="7">
+        <v>4.437313432835821</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>16.705554901960785</v>
+      </c>
+      <c r="R13" s="8">
+        <v>5.5127450980392156</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.45098039215686275</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -7603,7 +7655,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7633,35 +7685,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>2130.6100000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>21</v>
+      </c>
+      <c r="O42" s="6">
+        <v>17</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.2587285714285716</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>18.485294117647058</v>
+      </c>
+      <c r="R42" s="8">
+        <v>5.13958125</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -10025,7 +10135,9 @@
       <c r="N58" s="6">
         <v>47</v>
       </c>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>31</v>
+      </c>
       <c r="P58" s="7">
         <v>3.3507400000000001</v>
       </c>
@@ -10035,31 +10147,75 @@
       <c r="R58" s="8">
         <v>7.8086032258064515</v>
       </c>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9">
         <v>0.32258064516129031</v>
       </c>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -12635,7 +12791,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12663,35 +12819,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>4404.8299999999999</v>
+      </c>
+      <c r="N76" s="6">
+        <v>53</v>
+      </c>
+      <c r="O76" s="6">
+        <v>30</v>
+      </c>
+      <c r="P76" s="7">
+        <v>3.7336471698113205</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>15.708333333333334</v>
+      </c>
+      <c r="R76" s="8">
+        <v>4.079332</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -27916,7 +28130,9 @@
       <c r="N179" s="6">
         <v>60</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>21</v>
+      </c>
       <c r="P179" s="7">
         <v>4.5192084745762715</v>
       </c>
@@ -27926,31 +28142,75 @@
       <c r="R179" s="8">
         <v>1.861904761904762</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.80952380952380953</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
@@ -33022,43 +33282,43 @@
         <v>323</v>
       </c>
       <c t="s" r="AC216" s="11">
+        <v>323</v>
+      </c>
+      <c t="s" r="AD216" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AD216" s="11">
+      <c t="s" r="AE216" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AE216" s="11">
+      <c t="s" r="AF216" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AF216" s="11">
+      <c t="s" r="AG216" s="11">
         <v>327</v>
       </c>
-      <c t="s" r="AG216" s="11">
+      <c t="s" r="AH216" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AH216" s="11">
+      <c t="s" r="AI216" s="11">
         <v>329</v>
       </c>
-      <c t="s" r="AI216" s="11">
+      <c t="s" r="AJ216" s="11">
+        <v>327</v>
+      </c>
+      <c t="s" r="AK216" s="11">
         <v>330</v>
       </c>
-      <c t="s" r="AJ216" s="11">
-        <v>328</v>
-      </c>
-      <c t="s" r="AK216" s="11">
+      <c t="s" r="AL216" s="11">
         <v>331</v>
       </c>
-      <c t="s" r="AL216" s="11">
+      <c t="s" r="AM216" s="11">
+        <v>331</v>
+      </c>
+      <c t="s" r="AN216" s="11">
         <v>332</v>
       </c>
-      <c t="s" r="AM216" s="11">
+      <c t="s" r="AO216" s="11">
         <v>333</v>
-      </c>
-      <c t="s" r="AN216" s="11">
-        <v>334</v>
-      </c>
-      <c t="s" r="AO216" s="11">
-        <v>335</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33075,10 +33335,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-21).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-21).xlsx
@@ -935,13 +935,13 @@
     <t>214</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 3.070,92</t>
-  </si>
-  <si>
-    <t>35.1</t>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 3.068,17</t>
+  </si>
+  <si>
+    <t>35.0</t>
   </si>
   <si>
     <t>21.9</t>
@@ -950,7 +950,7 @@
     <t>4.68</t>
   </si>
   <si>
-    <t>17.9</t>
+    <t>18.0</t>
   </si>
   <si>
     <t>6.6</t>
@@ -4949,7 +4949,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4979,14 +4979,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>3054.5799999999999</v>
+      </c>
+      <c r="N24" s="6">
+        <v>33</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>3.4479156249999998</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>21.580953571428573</v>
+      </c>
+      <c r="R24" s="8">
+        <v>12.015433333333332</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.035714285714285712</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -14764,7 +14776,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14792,14 +14804,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>2577.8699999999999</v>
+      </c>
+      <c r="N89" s="6">
+        <v>23</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>4.8812500000000005</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>19.962118181818184</v>
+      </c>
+      <c r="R89" s="8">
+        <v>6.463636363636363</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.090909090909090912</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-21).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-21).xlsx
@@ -935,19 +935,19 @@
     <t>214</t>
   </si>
   <si>
-    <t>27</t>
+    <t>22</t>
   </si>
   <si>
-    <t>R$ 3.068,17</t>
+    <t>R$ 3.046,24</t>
   </si>
   <si>
-    <t>35.0</t>
+    <t>34.8</t>
   </si>
   <si>
     <t>21.9</t>
   </si>
   <si>
-    <t>4.68</t>
+    <t>4.69</t>
   </si>
   <si>
     <t>18.0</t>
@@ -956,16 +956,16 @@
     <t>6.6</t>
   </si>
   <si>
-    <t>6.1</t>
+    <t>6.3</t>
   </si>
   <si>
-    <t>45.3%</t>
+    <t>45.8%</t>
   </si>
   <si>
     <t>19.0%</t>
   </si>
   <si>
-    <t>2.1%</t>
+    <t>2.0%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -974,19 +974,22 @@
     <t>5.3%</t>
   </si>
   <si>
-    <t>1.2%</t>
+    <t>1.3%</t>
   </si>
   <si>
-    <t>7.6%</t>
+    <t>7.7%</t>
   </si>
   <si>
     <t>3.3%</t>
   </si>
   <si>
-    <t>933.0</t>
+    <t>3.2%</t>
   </si>
   <si>
-    <t>754.0</t>
+    <t>963.0</t>
+  </si>
+  <si>
+    <t>777.0</t>
   </si>
   <si>
     <t>82.0</t>
@@ -995,13 +998,16 @@
     <t>8.0</t>
   </si>
   <si>
-    <t>211.0</t>
+    <t>218.0</t>
   </si>
   <si>
-    <t>49.0</t>
+    <t>53.0</t>
   </si>
   <si>
-    <t>301.0</t>
+    <t>317.0</t>
+  </si>
+  <si>
+    <t>134.0</t>
   </si>
   <si>
     <t>131.0</t>
@@ -2197,7 +2203,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2227,35 +2233,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>4032.9299999999998</v>
+      </c>
+      <c r="N6" s="6">
+        <v>51</v>
+      </c>
+      <c r="O6" s="6">
+        <v>44</v>
+      </c>
+      <c r="P6" s="7">
+        <v>4.2794117647058822</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>12.92348409090909</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.4583340909090909</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.88636363636363635</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.068181818181818177</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -6785,7 +6849,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6815,35 +6879,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>2147.21</v>
+      </c>
+      <c r="N36" s="6">
+        <v>27</v>
+      </c>
+      <c r="O36" s="6">
+        <v>18</v>
+      </c>
+      <c r="P36" s="7">
+        <v>7.2888888888888896</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>13.817594444444445</v>
+      </c>
+      <c r="R36" s="8">
+        <v>2.9125000000000001</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7088,7 +7210,7 @@
         <v>2.5203666666666664</v>
       </c>
       <c r="S38" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" s="9">
         <v>1</v>
@@ -9074,7 +9196,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9104,35 +9226,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>511</v>
+      </c>
+      <c r="N51" s="6">
+        <v>5</v>
+      </c>
+      <c r="O51" s="6">
+        <v>1</v>
+      </c>
+      <c r="P51" s="7">
+        <v>3.7766599999999997</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>33.616700000000002</v>
+      </c>
+      <c r="R51" s="8">
+        <v>24.216699999999999</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -16701,7 +16881,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -16731,35 +16911,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>2201.4499999999998</v>
+      </c>
+      <c r="N102" s="6">
+        <v>24</v>
+      </c>
+      <c r="O102" s="6">
+        <v>16</v>
+      </c>
+      <c r="P102" s="7">
+        <v>6.3201375000000004</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>16.018750000000001</v>
+      </c>
+      <c r="R102" s="8">
+        <v>5.4606090909090907</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.5625</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -25001,7 +25239,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25031,35 +25269,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>2281.6999999999998</v>
+      </c>
+      <c r="N158" s="6">
+        <v>23</v>
+      </c>
+      <c r="O158" s="6">
+        <v>21</v>
+      </c>
+      <c r="P158" s="7">
+        <v>4.0847208333333329</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>12.964285714285714</v>
+      </c>
+      <c r="R158" s="8">
+        <v>1.8214285714285714</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -30496,7 +30792,9 @@
       <c r="N195" s="6">
         <v>34</v>
       </c>
-      <c r="O195" s="6"/>
+      <c r="O195" s="6">
+        <v>23</v>
+      </c>
       <c r="P195" s="7">
         <v>5.1057281249999997</v>
       </c>
@@ -30506,31 +30804,75 @@
       <c r="R195" s="8">
         <v>3.9586956521739127</v>
       </c>
-      <c r="S195" s="8"/>
+      <c r="S195" s="8">
+        <v>7</v>
+      </c>
       <c r="T195" s="9">
         <v>0.47826086956521741</v>
       </c>
-      <c r="U195" s="9"/>
-      <c r="V195" s="9"/>
-      <c r="W195" s="9"/>
-      <c r="X195" s="9"/>
-      <c r="Y195" s="9"/>
-      <c r="Z195" s="9"/>
-      <c r="AA195" s="9"/>
-      <c r="AB195" s="9"/>
-      <c r="AC195" s="9"/>
-      <c r="AD195" s="6"/>
-      <c r="AE195" s="6"/>
-      <c r="AF195" s="6"/>
-      <c r="AG195" s="6"/>
-      <c r="AH195" s="6"/>
-      <c r="AI195" s="6"/>
-      <c r="AJ195" s="6"/>
-      <c r="AK195" s="6"/>
-      <c r="AL195" s="6"/>
-      <c r="AM195" s="6"/>
-      <c r="AN195" s="9"/>
-      <c r="AO195" s="6"/>
+      <c r="U195" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="V195" s="9">
+        <v>0</v>
+      </c>
+      <c r="W195" s="9">
+        <v>0</v>
+      </c>
+      <c r="X195" s="9">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="Y195" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM195" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN195" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO195" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP195" s="4">
         <v>58</v>
       </c>
@@ -33306,43 +33648,43 @@
         <v>323</v>
       </c>
       <c t="s" r="AC216" s="11">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="AD216" s="11">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="AE216" s="11">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="AF216" s="11">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="AG216" s="11">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="AH216" s="11">
+        <v>329</v>
+      </c>
+      <c t="s" r="AI216" s="11">
+        <v>330</v>
+      </c>
+      <c t="s" r="AJ216" s="11">
         <v>328</v>
       </c>
-      <c t="s" r="AI216" s="11">
-        <v>329</v>
-      </c>
-      <c t="s" r="AJ216" s="11">
-        <v>327</v>
-      </c>
       <c t="s" r="AK216" s="11">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="AL216" s="11">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="AM216" s="11">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c t="s" r="AN216" s="11">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="AO216" s="11">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AP216" s="12"/>
       <c t="s" r="AQ216" s="12">
@@ -33359,10 +33701,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX216" s="11">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="AY216" s="11">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AZ216" s="12"/>
       <c r="BA216" s="12"/>
